--- a/frontend/frontend test/frontend_test_results.xlsx
+++ b/frontend/frontend test/frontend_test_results.xlsx
@@ -607,11 +607,11 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -687,11 +687,11 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.26</v>
+        <v>2.23</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3.08</v>
+        <v>1.22</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -847,11 +847,11 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.09</v>
+        <v>1.84</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -967,11 +967,11 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.49</v>
+        <v>1.36</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3.16</v>
+        <v>1.92</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1167,11 +1167,11 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2.95</v>
+        <v>1.34</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1327,11 +1327,11 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.23</v>
+        <v>0.99</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1407,11 +1407,11 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1527,11 +1527,11 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2.8</v>
+        <v>0.87</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.97</v>
+        <v>1.86</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1.44</v>
+        <v>3.18</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1687,11 +1687,11 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1767,11 +1767,11 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.31</v>
+        <v>0.79</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1807,11 +1807,11 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.28</v>
+        <v>3.07</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1887,11 +1887,11 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2.94</v>
+        <v>1.4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2007,11 +2007,11 @@
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.21</v>
+        <v>2.93</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2047,11 +2047,11 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2167,11 +2167,11 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2247,11 +2247,11 @@
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2287,11 +2287,11 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.98</v>
+        <v>2.67</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2327,11 +2327,11 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1.35</v>
+        <v>3.24</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2367,11 +2367,11 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1.4</v>
+        <v>2.19</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2447,11 +2447,11 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2487,11 +2487,11 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2527,11 +2527,11 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.07</v>
+        <v>0.76</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2567,11 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.84</v>
+        <v>2.66</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2607,11 +2607,11 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2647,11 +2647,11 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2.33</v>
+        <v>0.99</v>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2767,11 +2767,11 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2807,11 +2807,11 @@
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.92</v>
+        <v>3.21</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2847,11 +2847,11 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2.88</v>
+        <v>0.85</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2887,11 +2887,11 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.41</v>
+        <v>2.37</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3047,11 +3047,11 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3087,11 +3087,11 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3127,11 +3127,11 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3167,11 +3167,11 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.84</v>
+        <v>1.64</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3207,11 +3207,11 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2.16</v>
+        <v>2.96</v>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3287,11 +3287,11 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>3.01</v>
+        <v>2.02</v>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3327,11 +3327,11 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3367,11 +3367,11 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.91</v>
+        <v>1.84</v>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3407,11 +3407,11 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.43</v>
+        <v>2.72</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3447,11 +3447,11 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2.84</v>
+        <v>1.18</v>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3487,11 +3487,11 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.17</v>
+        <v>2.65</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3527,11 +3527,11 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3567,11 +3567,11 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3607,11 +3607,11 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3647,11 +3647,11 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2.07</v>
+        <v>3.23</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3687,11 +3687,11 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3727,11 +3727,11 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>3.05</v>
+        <v>1.22</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3767,11 +3767,11 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2.34</v>
+        <v>0.92</v>
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3807,11 +3807,11 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.37</v>
+        <v>2.59</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3847,11 +3847,11 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>3.07</v>
+        <v>2.21</v>
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3927,11 +3927,11 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -3967,11 +3967,11 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>1.37</v>
+        <v>0.95</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4007,11 +4007,11 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.66</v>
+        <v>2.97</v>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4047,11 +4047,11 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4087,11 +4087,11 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2.17</v>
+        <v>1.22</v>
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4127,11 +4127,11 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>1.04</v>
+        <v>2.77</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4167,11 +4167,11 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4207,11 +4207,11 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4247,11 +4247,11 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1.38</v>
+        <v>0.92</v>
       </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4287,11 +4287,11 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2.29</v>
+        <v>1.1</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4327,11 +4327,11 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1.44</v>
+        <v>2.94</v>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4367,11 +4367,11 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4407,11 +4407,11 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>2.71</v>
+        <v>1.21</v>
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4447,11 +4447,11 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>2.92</v>
+        <v>1.64</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4527,11 +4527,11 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4567,11 +4567,11 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>2.34</v>
+        <v>3.16</v>
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4607,11 +4607,11 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4647,11 +4647,11 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4687,11 +4687,11 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4727,11 +4727,11 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.61</v>
+        <v>0.78</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4807,11 +4807,11 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4847,11 +4847,11 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.69</v>
+        <v>2.35</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4887,11 +4887,11 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.66</v>
+        <v>3.08</v>
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4927,11 +4927,11 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -4967,11 +4967,11 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>1.75</v>
+        <v>2.41</v>
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5007,11 +5007,11 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5047,11 +5047,11 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5087,11 +5087,11 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5127,11 +5127,11 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>3.12</v>
+        <v>1.83</v>
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5167,11 +5167,11 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5207,11 +5207,11 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5247,11 +5247,11 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5287,11 +5287,11 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5327,11 +5327,11 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5367,11 +5367,11 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5407,11 +5407,11 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5447,11 +5447,11 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5487,11 +5487,11 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5527,11 +5527,11 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5567,11 +5567,11 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5607,11 +5607,11 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="H127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5647,11 +5647,11 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5687,11 +5687,11 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1.66</v>
+        <v>2.77</v>
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5727,11 +5727,11 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2.28</v>
+        <v>0.76</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5767,11 +5767,11 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.55</v>
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5807,11 +5807,11 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.95</v>
+        <v>2.17</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5847,11 +5847,11 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>3.22</v>
+        <v>2.03</v>
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5887,11 +5887,11 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5927,11 +5927,11 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2.08</v>
+        <v>0.78</v>
       </c>
       <c r="H135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -5967,11 +5967,11 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6007,11 +6007,11 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>2.23</v>
+        <v>2.58</v>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6047,11 +6047,11 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6087,11 +6087,11 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="H139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6127,11 +6127,11 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.93</v>
+        <v>2.14</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6167,11 +6167,11 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1.02</v>
+        <v>1.79</v>
       </c>
       <c r="H141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6207,11 +6207,11 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.87</v>
+        <v>3.23</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6247,11 +6247,11 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1.87</v>
+        <v>0.9</v>
       </c>
       <c r="H143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6287,11 +6287,11 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.08</v>
+        <v>2.58</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6327,11 +6327,11 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>2.69</v>
+        <v>1.68</v>
       </c>
       <c r="H145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6367,11 +6367,11 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>2.67</v>
+        <v>2.19</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6407,11 +6407,11 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>2.86</v>
+        <v>0.84</v>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6447,11 +6447,11 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6487,11 +6487,11 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="H149" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6527,11 +6527,11 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.77</v>
+        <v>2.48</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6567,11 +6567,11 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6607,11 +6607,11 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6647,11 +6647,11 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1.51</v>
+        <v>2.99</v>
       </c>
       <c r="H153" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6687,11 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6727,11 +6727,11 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>2.92</v>
+        <v>2.07</v>
       </c>
       <c r="H155" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6767,11 +6767,11 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.1</v>
+        <v>2.81</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6807,11 +6807,11 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.86</v>
+        <v>2.78</v>
       </c>
       <c r="H157" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6847,11 +6847,11 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6887,11 +6887,11 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6927,11 +6927,11 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -6967,11 +6967,11 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7007,11 +7007,11 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.98</v>
+        <v>1.29</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7047,11 +7047,11 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="H163" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7087,11 +7087,11 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7127,11 +7127,11 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="H165" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7167,11 +7167,11 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7207,11 +7207,11 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="H167" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7247,11 +7247,11 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7287,11 +7287,11 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7327,11 +7327,11 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>2.69</v>
+        <v>1.46</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7367,11 +7367,11 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7407,11 +7407,11 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7447,11 +7447,11 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7487,11 +7487,11 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.8</v>
+        <v>3.11</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7527,11 +7527,11 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7567,11 +7567,11 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.93</v>
+        <v>3.16</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7607,11 +7607,11 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7647,11 +7647,11 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7687,11 +7687,11 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>1.1</v>
+        <v>2.18</v>
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>2.77</v>
+        <v>1.88</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7767,11 +7767,11 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7807,11 +7807,11 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7847,11 +7847,11 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7887,11 +7887,11 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>2.11</v>
+        <v>2.67</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7927,11 +7927,11 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -7967,11 +7967,11 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>1.92</v>
+        <v>2.81</v>
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8047,11 +8047,11 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>2.34</v>
+        <v>3.07</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8087,11 +8087,11 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8127,11 +8127,11 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.76</v>
+        <v>1.75</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8167,11 +8167,11 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2.69</v>
+        <v>1.18</v>
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8207,11 +8207,11 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8247,11 +8247,11 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8287,11 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>2.73</v>
+        <v>1.43</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8327,11 +8327,11 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8367,11 +8367,11 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>3.24</v>
+        <v>1.92</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8407,11 +8407,11 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8447,11 +8447,11 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8487,11 +8487,11 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>0.89</v>
+        <v>2.72</v>
       </c>
       <c r="H199" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8527,11 +8527,11 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>2.51</v>
+        <v>1.43</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8567,11 +8567,11 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>3.13</v>
+        <v>1.65</v>
       </c>
       <c r="H201" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8607,11 +8607,11 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8647,11 +8647,11 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="H203" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8687,11 +8687,11 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8727,11 +8727,11 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="H205" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8767,11 +8767,11 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>2.45</v>
+        <v>0.78</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8807,11 +8807,11 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1.58</v>
+        <v>2.21</v>
       </c>
       <c r="H207" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8847,11 +8847,11 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>2.1</v>
+        <v>3.07</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8887,11 +8887,11 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="H209" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8927,11 +8927,11 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.19</v>
+        <v>2.72</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -8967,11 +8967,11 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1.49</v>
+        <v>0.83</v>
       </c>
       <c r="H211" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9007,11 +9007,11 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9047,11 +9047,11 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>2.89</v>
+        <v>1</v>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9087,11 +9087,11 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9127,11 +9127,11 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="H215" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9167,11 +9167,11 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.52</v>
+        <v>0.93</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9207,11 +9207,11 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1.27</v>
+        <v>3.15</v>
       </c>
       <c r="H217" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9247,11 +9247,11 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>3.15</v>
+        <v>1.19</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9287,11 +9287,11 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="H219" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9327,11 +9327,11 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.18</v>
+        <v>2.21</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9367,11 +9367,11 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>0.9</v>
+        <v>3.22</v>
       </c>
       <c r="H221" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9407,11 +9407,11 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9447,11 +9447,11 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>2.29</v>
+        <v>1.07</v>
       </c>
       <c r="H223" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9487,11 +9487,11 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9527,11 +9527,11 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="H225" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9567,11 +9567,11 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.82</v>
+        <v>2.64</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9607,11 +9607,11 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="H227" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9647,11 +9647,11 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>3.04</v>
+        <v>2.24</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9687,11 +9687,11 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="H229" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9727,11 +9727,11 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>1.1</v>
+        <v>1.63</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9767,11 +9767,11 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="H231" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9807,11 +9807,11 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>1.59</v>
+        <v>0.92</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9847,11 +9847,11 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="H233" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9887,11 +9887,11 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.35</v>
+        <v>0.79</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9927,11 +9927,11 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="H235" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -9967,11 +9967,11 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>2.69</v>
+        <v>1.72</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10007,11 +10007,11 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>2.09</v>
+        <v>1.04</v>
       </c>
       <c r="H237" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10087,11 +10087,11 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="H239" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10127,11 +10127,11 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10167,11 +10167,11 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>3.01</v>
+        <v>1.69</v>
       </c>
       <c r="H241" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10207,11 +10207,11 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10247,11 +10247,11 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="H243" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10287,11 +10287,11 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>2.79</v>
+        <v>1.46</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10327,11 +10327,11 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10367,11 +10367,11 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>2.55</v>
+        <v>1.54</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10407,11 +10407,11 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>3.19</v>
+        <v>1.71</v>
       </c>
       <c r="H247" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10447,11 +10447,11 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10487,11 +10487,11 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="H249" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10527,11 +10527,11 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>2.71</v>
+        <v>2.23</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10567,11 +10567,11 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="H251" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10607,11 +10607,11 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10647,11 +10647,11 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10687,11 +10687,11 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>3.14</v>
+        <v>2.15</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10727,11 +10727,11 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>3.07</v>
+        <v>1.2</v>
       </c>
       <c r="H255" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10767,11 +10767,11 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>1.8</v>
+        <v>0.99</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10807,11 +10807,11 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>1.24</v>
+        <v>0.95</v>
       </c>
       <c r="H257" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10847,11 +10847,11 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10887,11 +10887,11 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H259" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10927,11 +10927,11 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -10967,11 +10967,11 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="H261" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11007,11 +11007,11 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11047,11 +11047,11 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>1.19</v>
+        <v>2.44</v>
       </c>
       <c r="H263" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11087,11 +11087,11 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>2.95</v>
+        <v>1.48</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11127,11 +11127,11 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>1.93</v>
+        <v>2.69</v>
       </c>
       <c r="H265" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11167,11 +11167,11 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.96</v>
+        <v>3.2</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11207,11 +11207,11 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="H267" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11247,11 +11247,11 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11287,11 +11287,11 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>3.01</v>
+        <v>1.8</v>
       </c>
       <c r="H269" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11327,11 +11327,11 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>2.73</v>
+        <v>2.11</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11367,11 +11367,11 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="H271" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11407,11 +11407,11 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>1.73</v>
+        <v>0.76</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11447,11 +11447,11 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>2.06</v>
+        <v>1.1</v>
       </c>
       <c r="H273" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11487,11 +11487,11 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.03</v>
+        <v>3.16</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11527,11 +11527,11 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="H275" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11567,11 +11567,11 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11607,11 +11607,11 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>2.51</v>
+        <v>2.83</v>
       </c>
       <c r="H277" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11647,11 +11647,11 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11687,11 +11687,11 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>1.28</v>
+        <v>2.56</v>
       </c>
       <c r="H279" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11727,11 +11727,11 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>2.89</v>
+        <v>0.9</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11767,11 +11767,11 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>2.61</v>
+        <v>1.21</v>
       </c>
       <c r="H281" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11807,11 +11807,11 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11847,11 +11847,11 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>2.67</v>
+        <v>2.01</v>
       </c>
       <c r="H283" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11887,11 +11887,11 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>3.14</v>
+        <v>2.07</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11927,11 +11927,11 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H285" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -11967,11 +11967,11 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12007,11 +12007,11 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="H287" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12047,11 +12047,11 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12087,11 +12087,11 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>2.96</v>
+        <v>2.21</v>
       </c>
       <c r="H289" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12127,11 +12127,11 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>2.87</v>
+        <v>0.89</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12167,11 +12167,11 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="H291" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12207,11 +12207,11 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12247,11 +12247,11 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>2.86</v>
+        <v>1.37</v>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12287,11 +12287,11 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12327,11 +12327,11 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="H295" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12367,11 +12367,11 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12407,11 +12407,11 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>2.43</v>
+        <v>1.58</v>
       </c>
       <c r="H297" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12447,11 +12447,11 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12487,11 +12487,11 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H299" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12527,11 +12527,11 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>1.78</v>
+        <v>3.14</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12567,11 +12567,11 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>2.65</v>
+        <v>1.84</v>
       </c>
       <c r="H301" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:24:47</t>
+          <t>2026-08-01 13:37:12</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-01 13:24:47</t>
+          <t>Execution Date: 2026-08-01 13:37:13</t>
         </is>
       </c>
     </row>
